--- a/outputs/abdev_lite_results.xlsx
+++ b/outputs/abdev_lite_results.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Cleaned" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sequence_QC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chain_Properties" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Numbering_Residues" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Region_Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liability_Sites" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liability_Region_Map" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chain_Risk_Scores" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Humanness_Results" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Antibody_Summary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Input_Cleaned" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sequence_QC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chain_Properties" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Numbering_Residues" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Region_Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Liability_Sites" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Liability_Region_Map" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Chain_Risk_Scores" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Humanness_Results" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Antibody_Summary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Candidate_Ranking" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1912,6 +1913,492 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>antibody_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>molecule_format</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>number_of_chains</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>total_risk_score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cdr_adjusted_total_risk_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>max_chain_risk_class</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>cdr_adjusted_max_risk_class</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total_cdr_liabilities</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>total_fr_liabilities</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_humanness_risk_class</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>high_humanness_risk_chain_count</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>non_human_like_chain_count</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>combined_developability_humanness_flag</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>final_priority_score</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>final_priority_class</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>decision_label</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>review_reason</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>next_step_recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Developability review recommended</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Deprioritize or redesign before progression</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>High CDR-adjusted developability burden; Sequence-level hydrophobic patch proxy detected</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BadSeq001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Developability review recommended</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Deprioritize or redesign before progression</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>High CDR-adjusted developability burden; Sequence-level hydrophobic patch proxy detected</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BsAb</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>High priority engineering review</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Deprioritize or redesign before progression</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>High humanness risk based on imported assessment; High CDR-adjusted developability burden; Sequence-level hydrophobic patch proxy detected</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Full001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Developability review recommended</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Deprioritize or redesign before progression</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>High CDR-adjusted developability burden</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VHH001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VHH</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>High priority engineering review</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Deprioritize or redesign before progression</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>High humanness risk based on imported assessment; High CDR-adjusted developability burden; Sequence-level hydrophobic patch proxy detected</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3651,7 +4138,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3722,7 +4209,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3793,7 +4280,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3864,7 +4351,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3935,7 +4422,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -4006,7 +4493,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -4077,7 +4564,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4148,7 +4635,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">

--- a/outputs/abdev_lite_results.xlsx
+++ b/outputs/abdev_lite_results.xlsx
@@ -18,6 +18,9 @@
     <sheet name="Humanness_Results" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Antibody_Summary" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Candidate_Ranking" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Formulation_Features" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Expreso_Predictions" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Formulation_Recommendations" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2399,6 +2402,1564 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>antibody_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>molecule_format</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>number_of_chains</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>average_sequence_length</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>total_sequence_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>average_theoretical_pI</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>max_theoretical_pI</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>min_theoretical_pI</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>average_gravy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_gravy</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>average_instability_index</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>total_cysteine_count</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>total_methionine_count</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>total_tryptophan_count</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>total_asparagine_count</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>total_aspartic_acid_count</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>total_lysine_count</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>total_arginine_count</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>hydrophobic_residue_fraction_mean</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>aromatic_residue_fraction_mean</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>positive_residue_fraction_mean</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>negative_residue_fraction_mean</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>total_risk_score</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>cdr_adjusted_total_risk_score</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>total_cdr_liabilities</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>total_fr_liabilities</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>total_nglycosylation_motifs</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>total_deamidation_motifs</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>total_isomerization_motifs</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>total_oxidation_motifs</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>total_hydrophobic_patch_proxy</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>max_humanness_risk_class</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>final_priority_class</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>final_priority_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>221</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8.541499999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.036</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.047000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.2948</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.1877</v>
+      </c>
+      <c r="K2" t="n">
+        <v>40.473</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1084</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.0678</v>
+      </c>
+      <c r="W2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BadSeq001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.773</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.2273</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="W3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BsAb</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>446</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7.5555</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.981</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.337</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.3484</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.2453</v>
+      </c>
+      <c r="K4" t="n">
+        <v>39.9902</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O4" t="n">
+        <v>16</v>
+      </c>
+      <c r="P4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R4" t="n">
+        <v>23</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1252</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.08740000000000001</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="W4" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Full001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>227</v>
+      </c>
+      <c r="E5" t="n">
+        <v>227</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.808999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.808999999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.808999999999999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.1692</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.1692</v>
+      </c>
+      <c r="K5" t="n">
+        <v>45.005</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="W5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VHH001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VHH</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>115</v>
+      </c>
+      <c r="E6" t="n">
+        <v>115</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.638999999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.638999999999999</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.638999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.2504</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.2504</v>
+      </c>
+      <c r="K6" t="n">
+        <v>31.669</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1217</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="W6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>antibody_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>model_available</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>model_status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>prediction_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>recommended_buffer_ph_modifier_probability</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sugar_stabilizer_probability</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>polyol_stabilizer_probability</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>surfactant_probability</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>amino_acid_stabilizer_probability</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>antioxidant_probability</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>chelating_agent_probability</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>salt_ionic_strength_modifier_probability</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>preservative_probability</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>expreso_prediction_warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="B2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>model_not_found</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>rule_based_fallback</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Expreso-lite model files were not found. Rule-based fallback recommendation was used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BadSeq001</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>model_not_found</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>rule_based_fallback</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Expreso-lite model files were not found. Rule-based fallback recommendation was used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>model_not_found</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>rule_based_fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Expreso-lite model files were not found. Rule-based fallback recommendation was used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Full001</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>model_not_found</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>rule_based_fallback</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Expreso-lite model files were not found. Rule-based fallback recommendation was used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VHH001</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>model_not_found</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>rule_based_fallback</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Expreso-lite model files were not found. Rule-based fallback recommendation was used.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>antibody_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>formulation_risk_class</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>formulation_risk_score</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>recommended_excipient_classes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>top_excipient_class_1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>top_excipient_class_2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>top_excipient_class_3</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>buffer_ph_direction</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>surfactant_consideration</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sugar_polyol_consideration</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>oxidation_control_consideration</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ionic_strength_consideration</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>formulation_review_reason</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>formulation_next_step_recommendation</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>formulation_disclaimer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>sugar stabilizer; antioxidant; surfactant</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sugar stabilizer</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>antioxidant</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>surfactant</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Include broad buffer and pH screening; review pH-sensitive motifs</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Prioritize surfactant screening due to hydrophobicity signal</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Prioritize sugar/polyol stabilizer screening due to instability signal</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Consider antioxidant and oxidation-control review</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Optional ionic strength screen</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Elevated oxidation-prone residue count; Hydrophobicity or hydrophobic patch proxy suggests surfactant review; High CDR-adjusted developability burden; Instability index suggests stabilizer screening; Deamidation/isomerization motif burden suggests pH sensitivity review</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Prioritize preformulation risk review before scale-up or advanced developability studies</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Formulation recommendations are computational triage outputs based on sequence-level features and optional Expreso-lite model predictions. They are intended to support early preformulation planning only and do not replace experimental formulation screening, stability studies, or CMC evaluation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BadSeq001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>surfactant; buffer / pH modifier; antioxidant</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>surfactant</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>buffer / pH modifier</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>antioxidant</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Prioritize pH screening above the low theoretical pI range; review pH-sensitive motifs</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Prioritize surfactant screening due to hydrophobicity signal</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Consider sugar stabilizer as a default early screen</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Consider antioxidant and oxidation-control review</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Include ionic strength screen because theoretical pI is shifted</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Elevated oxidation-prone residue count; Hydrophobicity or hydrophobic patch proxy suggests surfactant review; High CDR-adjusted developability burden; Theoretical pI is outside the broad neutral range; Deamidation/isomerization motif burden suggests pH sensitivity review</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Prioritize preformulation risk review before scale-up or advanced developability studies</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Formulation recommendations are computational triage outputs based on sequence-level features and optional Expreso-lite model predictions. They are intended to support early preformulation planning only and do not replace experimental formulation screening, stability studies, or CMC evaluation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>antioxidant; surfactant; buffer / pH modifier</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>antioxidant</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>surfactant</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>buffer / pH modifier</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Include broad buffer and pH screening; review pH-sensitive motifs</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Prioritize surfactant screening due to hydrophobicity signal</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Consider sugar stabilizer as a default early screen</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Consider antioxidant and oxidation-control review</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Optional ionic strength screen</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Elevated oxidation-prone residue count; Hydrophobicity or hydrophobic patch proxy suggests surfactant review; High CDR-adjusted developability burden; Deamidation/isomerization motif burden suggests pH sensitivity review</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Prioritize preformulation risk review before scale-up or advanced developability studies</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Formulation recommendations are computational triage outputs based on sequence-level features and optional Expreso-lite model predictions. They are intended to support early preformulation planning only and do not replace experimental formulation screening, stability studies, or CMC evaluation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Full001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sugar stabilizer; antioxidant; surfactant</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sugar stabilizer</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>antioxidant</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>surfactant</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Include broad buffer and pH screening; review pH-sensitive motifs</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Prioritize surfactant screening due to hydrophobicity signal</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Prioritize sugar/polyol stabilizer screening due to instability signal</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Consider antioxidant and oxidation-control review</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Optional ionic strength screen</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Elevated oxidation-prone residue count; Hydrophobicity or hydrophobic patch proxy suggests surfactant review; High CDR-adjusted developability burden; Instability index suggests stabilizer screening; Deamidation/isomerization motif burden suggests pH sensitivity review; Cysteine count suggests redox-related review</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Prioritize preformulation risk review before scale-up or advanced developability studies</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Formulation recommendations are computational triage outputs based on sequence-level features and optional Expreso-lite model predictions. They are intended to support early preformulation planning only and do not replace experimental formulation screening, stability studies, or CMC evaluation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VHH001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>antioxidant; surfactant; buffer / pH modifier</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>antioxidant</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>surfactant</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>buffer / pH modifier</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Include broad buffer and pH screening; review pH-sensitive motifs</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Prioritize surfactant screening due to hydrophobicity signal</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Consider sugar stabilizer as a default early screen</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Consider antioxidant and oxidation-control review</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Optional ionic strength screen</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Elevated oxidation-prone residue count; Hydrophobicity or hydrophobic patch proxy suggests surfactant review; High CDR-adjusted developability burden; Deamidation/isomerization motif burden suggests pH sensitivity review</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Prioritize preformulation risk review before scale-up or advanced developability studies</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Formulation recommendations are computational triage outputs based on sequence-level features and optional Expreso-lite model predictions. They are intended to support early preformulation planning only and do not replace experimental formulation screening, stability studies, or CMC evaluation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/outputs/abdev_lite_results.xlsx
+++ b/outputs/abdev_lite_results.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Input_Cleaned" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sequence_QC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Chain_Properties" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Numbering_Residues" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Region_Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Liability_Sites" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Liability_Region_Map" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Chain_Risk_Scores" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Humanness_Results" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Antibody_Summary" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Candidate_Ranking" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Formulation_Features" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Expreso_Predictions" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Formulation_Recommendations" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Cleaned" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sequence_QC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chain_Properties" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Numbering_Residues" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Region_Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liability_Sites" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liability_Region_Map" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chain_Risk_Scores" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Humanness_Results" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Antibody_Summary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Ranking" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formulation_Features" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expreso_Predictions" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formulation_Recommendations" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure_Results" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structural_Risk_Summary" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,7 +1108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1270,6 +1272,31 @@
           <t>combined_developability_humanness_flag</t>
         </is>
       </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>structure_available</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>structural_risk_class</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>structural_risk_score</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>structural_review_reason</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>structural_next_step_recommendation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1355,7 +1382,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Input sequences passed basic QC; No obvious N-glycosylation motif detected in variable region; No obvious unpaired cysteine proxy detected; No obvious liability motif mapped to CDR regions by IMGT-based computational assignment; Human-likeness metrics suggest low humanness risk based on imported assessment</t>
+          <t>Input sequences passed basic QC; No obvious N-glycosylation motif detected in variable region; No obvious unpaired cysteine proxy detected; No obvious liability motif mapped to CDR regions by IMGT-based computational assignment; Human-likeness metrics suggest low humanness risk based on imported assessment; Imported structure metrics suggest low structural risk in this MVP assessment</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1400,6 +1427,27 @@
       <c r="AF2" t="inlineStr">
         <is>
           <t>Developability review recommended</t>
+        </is>
+      </c>
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>No major structural risk flag detected from imported metrics</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Imported structure metrics do not indicate a major structural review flag in this MVP assessment</t>
         </is>
       </c>
     </row>
@@ -1526,6 +1574,27 @@
           <t>Developability review recommended</t>
         </is>
       </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>No external structure prediction result was provided</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Import external structure prediction summary metrics if structural triage is needed</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1656,6 +1725,27 @@
       <c r="AF4" t="inlineStr">
         <is>
           <t>High priority engineering review</t>
+        </is>
+      </c>
+      <c r="AG4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>No major structural risk flag detected from imported metrics</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Review imported structure confidence and patch annotations before progression</t>
         </is>
       </c>
     </row>
@@ -1782,6 +1872,27 @@
           <t>Developability review recommended</t>
         </is>
       </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>No external structure prediction result was provided</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Import external structure prediction summary metrics if structural triage is needed</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1908,6 +2019,27 @@
       <c r="AF6" t="inlineStr">
         <is>
           <t>High priority engineering review</t>
+        </is>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>No external structure prediction result was provided</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Import external structure prediction summary metrics if structural triage is needed</t>
         </is>
       </c>
     </row>
@@ -1922,7 +2054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1993,25 +2125,40 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>structure_available</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>structural_risk_class</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>structural_risk_score</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>final_priority_score</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>final_priority_class</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>decision_label</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>review_reason</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>next_step_recommendation</t>
         </is>
@@ -2069,25 +2216,36 @@
           <t>Developability review recommended</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Deprioritize or redesign before progression</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>High CDR-adjusted developability burden; Sequence-level hydrophobic patch proxy detected</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
         </is>
@@ -2145,25 +2303,36 @@
           <t>Developability review recommended</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" t="b">
         <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Deprioritize or redesign before progression</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>High CDR-adjusted developability burden; Sequence-level hydrophobic patch proxy detected</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>High CDR-adjusted developability burden; No structure result imported; Sequence-level hydrophobic patch proxy detected</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
         </is>
@@ -2221,25 +2390,36 @@
           <t>High priority engineering review</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Deprioritize or redesign before progression</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>High humanness risk based on imported assessment; High CDR-adjusted developability burden; Sequence-level hydrophobic patch proxy detected</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
         </is>
@@ -2297,25 +2477,36 @@
           <t>Developability review recommended</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Deprioritize or redesign before progression</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>High CDR-adjusted developability burden</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>High CDR-adjusted developability burden; No structure result imported</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
         </is>
@@ -2373,25 +2564,36 @@
           <t>High priority engineering review</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" t="b">
         <v>0</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Deprioritize or redesign before progression</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>High humanness risk based on imported assessment; High CDR-adjusted developability burden; Sequence-level hydrophobic patch proxy detected</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>High humanness risk based on imported assessment; High CDR-adjusted developability burden; No structure result imported; Sequence-level hydrophobic patch proxy detected</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
         </is>
@@ -3960,6 +4162,854 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>antibody_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>chain_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sequence_scope</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>structure_tool</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>structure_model_file</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>structure_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mean_plddt</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cdr1_plddt</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>cdr2_plddt</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>cdr3_plddt</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>vh_vl_orientation_confidence</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>predicted_surface_hydrophobic_patch_score</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>predicted_aggregation_patch_score</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>predicted_charge_patch_score</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>structural_notes</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>merge_status</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>merge_warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VHVL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VH,VL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ab001_VHVL.pdb</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>86</v>
+      </c>
+      <c r="I2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Low structural risk example</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>matched_by_antibody_id</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ArmA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BsAb001_ArmA_model.pdb</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>76</v>
+      </c>
+      <c r="H3" t="n">
+        <v>74</v>
+      </c>
+      <c r="I3" t="n">
+        <v>72</v>
+      </c>
+      <c r="J3" t="n">
+        <v>71</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Medium structural risk example from orientation warning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>matched_by_antibody_id</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ab_CDR3Low</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ab_CDR3Low_VH.pdb</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>78</v>
+      </c>
+      <c r="H4" t="n">
+        <v>75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>73</v>
+      </c>
+      <c r="J4" t="n">
+        <v>55</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Low CDR3 pLDDT sample</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>No matching analyzed antibody or chain found for imported structure row</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ab_HydroPatch</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VHVL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VH,VL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ab_HydroPatch_VHVL.pdb</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>81</v>
+      </c>
+      <c r="H5" t="n">
+        <v>78</v>
+      </c>
+      <c r="I5" t="n">
+        <v>79</v>
+      </c>
+      <c r="J5" t="n">
+        <v>77</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>High hydrophobic patch score sample</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>No matching analyzed antibody or chain found for imported structure row</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ab_FAIL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ab_FAIL_failed_model.pdb</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>62</v>
+      </c>
+      <c r="H6" t="n">
+        <v>68</v>
+      </c>
+      <c r="I6" t="n">
+        <v>69</v>
+      </c>
+      <c r="J6" t="n">
+        <v>58</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Failed structure status sample</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>No matching analyzed antibody or chain found for imported structure row</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>antibody_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>structure_available</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>structure_tools</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>structure_model_files</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>structure_status_summary</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean_plddt_min</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mean_plddt_mean</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cdr1_plddt_min</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>cdr2_plddt_min</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>cdr3_plddt_min</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>low_confidence_cdr_count</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>high_hydrophobic_patch_flag</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>high_aggregation_patch_flag</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>high_charge_patch_flag</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>structural_risk_score</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>structural_risk_class</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>structural_review_reason</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>structural_next_step_recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ab001_VHVL.pdb</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PASS (1)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>86</v>
+      </c>
+      <c r="I2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>No major structural risk flag detected from imported metrics</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Imported structure metrics do not indicate a major structural review flag in this MVP assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BsAb001_ArmA_model.pdb</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WARNING (1)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G3" t="n">
+        <v>76</v>
+      </c>
+      <c r="H3" t="n">
+        <v>74</v>
+      </c>
+      <c r="I3" t="n">
+        <v>72</v>
+      </c>
+      <c r="J3" t="n">
+        <v>71</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>No major structural risk flag detected from imported metrics</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Review imported structure confidence and patch annotations before progression</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BadSeq001</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>No external structure prediction result was provided</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Import external structure prediction summary metrics if structural triage is needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Full001</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>No external structure prediction result was provided</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Import external structure prediction summary metrics if structural triage is needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VHH001</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>No external structure prediction result was provided</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Import external structure prediction summary metrics if structural triage is needed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5699,7 +6749,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IMGT numbering failed: No module named 'anarci'</t>
+          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -5770,7 +6820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IMGT numbering failed: No module named 'anarci'</t>
+          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -5841,7 +6891,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IMGT numbering failed: No module named 'anarci'</t>
+          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -5912,7 +6962,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IMGT numbering failed: No module named 'anarci'</t>
+          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -5983,7 +7033,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IMGT numbering failed: No module named 'anarci'</t>
+          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -6054,7 +7104,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IMGT numbering failed: No module named 'anarci'</t>
+          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -6125,7 +7175,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IMGT numbering failed: No module named 'anarci'</t>
+          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -6196,7 +7246,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IMGT numbering failed: No module named 'anarci'</t>
+          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">

--- a/outputs/abdev_lite_results.xlsx
+++ b/outputs/abdev_lite_results.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Cleaned" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sequence_QC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chain_Properties" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Numbering_Residues" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Region_Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liability_Sites" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liability_Region_Map" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chain_Risk_Scores" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Humanness_Results" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Antibody_Summary" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Ranking" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formulation_Features" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expreso_Predictions" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formulation_Recommendations" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure_Results" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structural_Risk_Summary" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Input_Cleaned" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sequence_QC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chain_Properties" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Numbering_Residues" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Region_Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Liability_Sites" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Liability_Region_Map" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Chain_Risk_Scores" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Humanness_Results" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Antibody_Summary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Candidate_Ranking" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Formulation_Features" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Expreso_Predictions" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Formulation_Recommendations" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Structure_Results" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Structural_Risk_Summary" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AbNumber/ANARCI is not available: No module named 'abnumber'</t>
+          <t>IMGT numbering failed: No module named 'anarci'</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">

--- a/outputs/abdev_lite_results.xlsx
+++ b/outputs/abdev_lite_results.xlsx
@@ -23,6 +23,10 @@
     <sheet name="Formulation_Recommendations" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Structure_Results" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Structural_Risk_Summary" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Tool_Registry" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="External_Tool_Run_Plan" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="External_Tool_Results" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="External_Tool_Summary" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1108,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,6 +1301,56 @@
           <t>structural_next_step_recommendation</t>
         </is>
       </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>external_tool_results_available</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>tools_with_results</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>humanness_tool_result_available</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>developability_tool_result_available</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>structure_tool_result_available</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>external_high_risk_flags</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>external_medium_risk_flags</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>external_low_risk_flags</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>external_tool_summary_text</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>external_tool_review_recommendation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1382,7 +1436,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Input sequences passed basic QC; No obvious N-glycosylation motif detected in variable region; No obvious unpaired cysteine proxy detected; No obvious liability motif mapped to CDR regions by IMGT-based computational assignment; Human-likeness metrics suggest low humanness risk based on imported assessment; Imported structure metrics suggest low structural risk in this MVP assessment</t>
+          <t>Input sequences passed basic QC; No obvious N-glycosylation motif detected in variable region; No obvious unpaired cysteine proxy detected; No obvious liability motif mapped to CDR regions by IMGT-based computational assignment; Imported structure metrics suggest low structural risk in this MVP assessment</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1396,23 +1450,15 @@
         </is>
       </c>
       <c r="Y2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>VH: Low; VL: Low</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>IGHV3-23; IGKV1-39</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
@@ -1421,7 +1467,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Imported humanness/germline assessment available for 2 chain(s); maximum conservative human-likeness risk class: Low. Human-likeness is not equivalent to clinical immunogenicity prediction.</t>
+          <t>No external humanness/germline assessment file was provided or matched.</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1450,6 +1496,38 @@
           <t>Imported structure metrics do not indicate a major structural review flag in this MVP assessment</t>
         </is>
       </c>
+      <c r="AL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1595,6 +1673,38 @@
           <t>Import external structure prediction summary metrics if structural triage is needed</t>
         </is>
       </c>
+      <c r="AL3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1680,12 +1790,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Input sequences passed basic QC; No obvious unpaired cysteine proxy detected; No obvious liability motif mapped to CDR regions by IMGT-based computational assignment</t>
+          <t>Input sequences passed basic QC; No obvious unpaired cysteine proxy detected; No obvious liability motif mapped to CDR regions by IMGT-based computational assignment; Imported structure metrics suggest low structural risk in this MVP assessment</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>N-glycosylation motif detected; Deamidation motif detected; Isomerization motif detected; Oxidation-prone residue detected; Long hydrophobic segment detected by sequence-level proxy; BsAb format detected. This MVP evaluates sequence-level liabilities of each variable region chain independently. It does not yet evaluate chain pairing, heterodimerization, Fc engineering, linker geometry, or full molecule architecture.; Imported humanness metrics suggest high human-likeness risk; humanization review may be needed</t>
+          <t>N-glycosylation motif detected; Deamidation motif detected; Isomerization motif detected; Oxidation-prone residue detected; Long hydrophobic segment detected by sequence-level proxy; BsAb format detected. This MVP evaluates sequence-level liabilities of each variable region chain independently. It does not yet evaluate chain pairing, heterodimerization, Fc engineering, linker geometry, or full molecule architecture.</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1694,37 +1804,29 @@
         </is>
       </c>
       <c r="Y4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>VH_arm1: Medium; VH_arm2: High</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>IGHV1-46; IGHV4-34</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Imported humanness/germline assessment available for 2 chain(s); maximum conservative human-likeness risk class: High. Human-likeness is not equivalent to clinical immunogenicity prediction.</t>
+          <t>No external humanness/germline assessment file was provided or matched.</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>High priority engineering review</t>
+          <t>Developability review recommended</t>
         </is>
       </c>
       <c r="AG4" t="b">
@@ -1732,11 +1834,11 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1745,7 +1847,39 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Review imported structure confidence and patch annotations before progression</t>
+          <t>Imported structure metrics do not indicate a major structural review flag in this MVP assessment</t>
+        </is>
+      </c>
+      <c r="AL4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
         </is>
       </c>
     </row>
@@ -1893,6 +2027,38 @@
           <t>Import external structure prediction summary metrics if structural triage is needed</t>
         </is>
       </c>
+      <c r="AL5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1978,12 +2144,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Input sequences passed basic QC; No obvious unpaired cysteine proxy detected; No obvious liability motif mapped to CDR regions by IMGT-based computational assignment</t>
+          <t>Input sequences passed basic QC; No obvious unpaired cysteine proxy detected; No obvious liability motif mapped to CDR regions by IMGT-based computational assignment; Imported structure metrics suggest low structural risk in this MVP assessment</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>N-glycosylation motif detected; Deamidation motif detected; Isomerization motif detected; Oxidation-prone residue detected; Long hydrophobic segment detected by sequence-level proxy; Imported humanness metrics suggest high human-likeness risk; humanization review may be needed</t>
+          <t>N-glycosylation motif detected; Deamidation motif detected; Isomerization motif detected; Oxidation-prone residue detected; Long hydrophobic segment detected by sequence-level proxy</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1992,41 +2158,37 @@
         </is>
       </c>
       <c r="Y6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>VHH: High</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>No external humanness/germline assessment file was provided or matched.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Developability review recommended</t>
+        </is>
+      </c>
+      <c r="AG6" t="b">
         <v>1</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Imported humanness/germline assessment available for 1 chain(s); maximum conservative human-likeness risk class: High. Human-likeness is not equivalent to clinical immunogenicity prediction.</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>High priority engineering review</t>
-        </is>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AI6" t="n">
@@ -2034,12 +2196,44 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>No external structure prediction result was provided</t>
+          <t>No major structural risk flag detected from imported metrics</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Import external structure prediction summary metrics if structural triage is needed</t>
+          <t>Imported structure metrics do not indicate a major structural review flag in this MVP assessment</t>
+        </is>
+      </c>
+      <c r="AL6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2140,25 +2334,40 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>external_high_risk_flags</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>external_medium_risk_flags</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>external_tool_results_available</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>final_priority_score</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>final_priority_class</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>decision_label</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>review_reason</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>next_step_recommendation</t>
         </is>
@@ -2167,22 +2376,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ab001</t>
+          <t>VHH001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mAb</t>
+          <t>VHH</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="E2" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2202,7 +2411,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -2230,22 +2439,31 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Deprioritize or redesign before progression</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>High CDR-adjusted developability burden; Sequence-level hydrophobic patch proxy detected</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>High CDR-adjusted developability burden; No external tool result imported; Sequence-level hydrophobic patch proxy detected</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
         </is>
@@ -2254,7 +2472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BadSeq001</t>
+          <t>Ab001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2263,52 +2481,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Developability review recommended</t>
+        </is>
+      </c>
+      <c r="N3" t="b">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
-        <v>21</v>
-      </c>
-      <c r="E3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Developability review recommended</t>
-        </is>
-      </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -2317,22 +2535,31 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Deprioritize or redesign before progression</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>High CDR-adjusted developability burden; No structure result imported; Sequence-level hydrophobic patch proxy detected</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>High CDR-adjusted developability burden; No external tool result imported; Sequence-level hydrophobic patch proxy detected</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
         </is>
@@ -2341,22 +2568,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BsAb001</t>
+          <t>BadSeq001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BsAb</t>
+          <t>mAb</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>43.5</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>43.5</v>
+        <v>21</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2376,50 +2603,59 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>High priority engineering review</t>
+          <t>Developability review recommended</t>
         </is>
       </c>
       <c r="N4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Deprioritize or redesign before progression</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>High humanness risk based on imported assessment; High CDR-adjusted developability burden; Sequence-level hydrophobic patch proxy detected</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>High CDR-adjusted developability burden; No structure result imported; No external tool result imported; Sequence-level hydrophobic patch proxy detected</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
         </is>
@@ -2428,61 +2664,61 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full001</t>
+          <t>BsAb001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mAb</t>
+          <t>BsAb</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Developability review recommended</t>
+        </is>
+      </c>
+      <c r="N5" t="b">
         <v>1</v>
       </c>
-      <c r="D5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Developability review recommended</t>
-        </is>
-      </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -2491,22 +2727,31 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Deprioritize or redesign before progression</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>High CDR-adjusted developability burden; No structure result imported</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>High CDR-adjusted developability burden; No external tool result imported; Sequence-level hydrophobic patch proxy detected</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
         </is>
@@ -2515,22 +2760,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VHH001</t>
+          <t>Full001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VHH</t>
+          <t>mAb</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="E6" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2550,18 +2795,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>High priority engineering review</t>
+          <t>Developability review recommended</t>
         </is>
       </c>
       <c r="N6" t="b">
@@ -2578,22 +2823,31 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Deprioritize or redesign before progression</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>High humanness risk based on imported assessment; High CDR-adjusted developability burden; No structure result imported; Sequence-level hydrophobic patch proxy detected</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>High CDR-adjusted developability burden; No structure result imported; No external tool result imported</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>Consider redesign, deprioritization, or additional humanization/developability review</t>
         </is>
@@ -2885,7 +3139,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -3109,7 +3363,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -3333,7 +3587,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -3342,7 +3596,7 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -4168,7 +4422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4266,61 +4520,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VHVL</t>
+          <t>VH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VH,VL</t>
+          <t>VH</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IgFold</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ab001_VHVL.pdb</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>86</v>
-      </c>
-      <c r="I2" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>82</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.3</v>
-      </c>
+          <t>&lt;NA&gt;</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Low structural risk example</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>matched_by_antibody_id</t>
+          <t>matched_by_antibody_id_sequence_scope</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -4333,61 +4571,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ArmA</t>
+          <t>VH1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VH</t>
+          <t>VH_arm1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BsAb001_ArmA_model.pdb</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>76</v>
-      </c>
-      <c r="H3" t="n">
-        <v>74</v>
-      </c>
-      <c r="I3" t="n">
-        <v>72</v>
-      </c>
-      <c r="J3" t="n">
-        <v>71</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.4</v>
-      </c>
+          <t>&lt;NA&gt;</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Medium structural risk example from orientation warning</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>matched_by_antibody_id</t>
+          <t>matched_by_antibody_id_sequence_scope</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -4395,213 +4617,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ab_CDR3Low</t>
+          <t>VHH001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VH</t>
+          <t>VHH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VH</t>
+          <t>VHH</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IgFold</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ab_CDR3Low_VH.pdb</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>78</v>
-      </c>
-      <c r="H4" t="n">
-        <v>75</v>
-      </c>
-      <c r="I4" t="n">
-        <v>73</v>
-      </c>
-      <c r="J4" t="n">
-        <v>55</v>
-      </c>
+          <t>&lt;NA&gt;</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.35</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Low CDR3 pLDDT sample</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>No matching analyzed antibody or chain found for imported structure row</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ab_HydroPatch</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>VHVL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VH,VL</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>IgFold</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Ab_HydroPatch_VHVL.pdb</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>81</v>
-      </c>
-      <c r="H5" t="n">
-        <v>78</v>
-      </c>
-      <c r="I5" t="n">
-        <v>79</v>
-      </c>
-      <c r="J5" t="n">
-        <v>77</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>High hydrophobic patch score sample</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>No matching analyzed antibody or chain found for imported structure row</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ab_FAIL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>VH</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VH</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ab_FAIL_failed_model.pdb</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>62</v>
-      </c>
-      <c r="H6" t="n">
-        <v>68</v>
-      </c>
-      <c r="I6" t="n">
-        <v>69</v>
-      </c>
-      <c r="J6" t="n">
-        <v>58</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Failed structure status sample</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>No matching analyzed antibody or chain found for imported structure row</t>
-        </is>
-      </c>
+          <t>matched_by_antibody_id_sequence_scope</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4720,34 +4782,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IgFold</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ab001_VHVL.pdb</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PASS (1)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>86</v>
-      </c>
-      <c r="I2" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>82</v>
-      </c>
+          <t>&lt;NA&gt; (1)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
@@ -4790,34 +4842,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BsAb001_ArmA_model.pdb</t>
+          <t>&lt;NA&gt;</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WARNING (1)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G3" t="n">
-        <v>76</v>
-      </c>
-      <c r="H3" t="n">
-        <v>74</v>
-      </c>
-      <c r="I3" t="n">
-        <v>72</v>
-      </c>
-      <c r="J3" t="n">
-        <v>71</v>
-      </c>
+          <t>&lt;NA&gt; (1)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>0</v>
       </c>
@@ -4831,11 +4873,11 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -4845,24 +4887,32 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Review imported structure confidence and patch annotations before progression</t>
+          <t>Imported structure metrics do not indicate a major structural review flag in this MVP assessment</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BadSeq001</t>
+          <t>VHH001</t>
         </is>
       </c>
       <c r="B4" t="b">
-        <v>0</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>&lt;NA&gt; (1)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -4887,24 +4937,24 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>No external structure prediction result was provided</t>
+          <t>No major structural risk flag detected from imported metrics</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Import external structure prediction summary metrics if structural triage is needed</t>
+          <t>Imported structure metrics do not indicate a major structural review flag in this MVP assessment</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full001</t>
+          <t>BadSeq001</t>
         </is>
       </c>
       <c r="B5" t="b">
@@ -4956,7 +5006,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VHH001</t>
+          <t>Full001</t>
         </is>
       </c>
       <c r="B6" t="b">
@@ -5002,6 +5052,2912 @@
       <c r="R6" t="inlineStr">
         <is>
           <t>Import external structure prediction summary metrics if structural triage is needed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>tool_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tool_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tool_category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>automation_allowed</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>supports_batch</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>supports_api</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>supports_cli</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>requires_web_upload</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>recommended_use</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>humanness</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Human-likeness and OASis-style humanness review.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Prepare FASTA locally, run manually according to tool terms, then import the result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IgBLAST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IgBLAST</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>germline</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Germline assignment and V(D)J annotation support.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Local CLI use is preferred when available; no browser automation is enabled by default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TAP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TAP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>developability</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>External developability flag review.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>User-managed export/import workflow only in v0.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Optional structure prediction evidence generated outside AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Import only summary-level user-provided structure evidence in this framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ImmuneBuilder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ImmuneBuilder</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Optional antibody structure model evidence generated outside AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Browser automation and credential handling are not implemented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Custom_Manual_Tool</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Custom Manual Tool</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>User-defined external computational evidence.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Generic manual export/import path for internal or user-defined tools.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>run_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tool_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tool_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>antibody_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>chain_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sequence_scope</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>input_file</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>input_format</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>run_mode</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>run_status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>user_action_required</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>run_instruction</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_Ab001_VH_FASTA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.fasta</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_Ab001_VH_CSV</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.csv</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_Ab001_VL_FASTA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.fasta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_Ab001_VL_CSV</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.csv</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_BsAb001_VH_arm1_FASTA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>VH_arm1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VH_arm1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.fasta</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_BsAb001_VH_arm1_CSV</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>VH_arm1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VH_arm1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.csv</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_BsAb001_VL_arm1_FASTA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>VL_arm1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VL_arm1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.fasta</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_BsAb001_VL_arm1_CSV</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>VL_arm1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VL_arm1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.csv</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_BsAb001_VH_arm2_FASTA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>VH_arm2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VH_arm2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.fasta</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_BsAb001_VH_arm2_CSV</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>VH_arm2</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VH_arm2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.csv</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_BsAb001_VL_arm2_FASTA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>VL_arm2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VL_arm2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.fasta</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_BsAb001_VL_arm2_CSV</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>VL_arm2</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VL_arm2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.csv</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_VHH001_VHH_FASTA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VHH001</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>VHH</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VHH</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.fasta</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_VHH001_VHH_CSV</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VHH001</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>VHH</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VHH</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.csv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_BadSeq001_VH_bad_FASTA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BadSeq001</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>VH_bad</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.fasta</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_BadSeq001_VH_bad_CSV</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BadSeq001</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>VH_bad</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.csv</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_Full001_full_heavy_FASTA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Full001</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>full_heavy</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>full_heavy</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.fasta</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis_Full001_full_heavy_CSV</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BioPhi_OASis</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BioPhi / OASis</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Full001</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>full_heavy</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>full_heavy</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>external_inputs\BioPhi_OASis\BioPhi_OASis_input.csv</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>manual_export_import</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IgFold_Ab001_VH_FASTA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.fasta</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IgFold_Ab001_VH_CSV</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.csv</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>IgFold_Ab001_VL_FASTA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.fasta</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>IgFold_Ab001_VL_CSV</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.csv</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>IgFold_BsAb001_VH_arm1_FASTA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>VH_arm1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VH_arm1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.fasta</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IgFold_BsAb001_VH_arm1_CSV</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>VH_arm1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VH_arm1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.csv</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IgFold_BsAb001_VL_arm1_FASTA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>VL_arm1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VL_arm1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.fasta</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IgFold_BsAb001_VL_arm1_CSV</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>VL_arm1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VL_arm1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.csv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IgFold_BsAb001_VH_arm2_FASTA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>VH_arm2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VH_arm2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.fasta</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IgFold_BsAb001_VH_arm2_CSV</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>VH_arm2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VH_arm2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.csv</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IgFold_BsAb001_VL_arm2_FASTA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>VL_arm2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VL_arm2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.fasta</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IgFold_BsAb001_VL_arm2_CSV</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>VL_arm2</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VL_arm2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.csv</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IgFold_VHH001_VHH_FASTA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VHH001</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VHH</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VHH</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.fasta</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>IgFold_VHH001_VHH_CSV</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VHH001</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VHH</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VHH</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.csv</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IgFold_BadSeq001_VH_bad_FASTA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BadSeq001</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>VH_bad</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.fasta</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>IgFold_BadSeq001_VH_bad_CSV</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BadSeq001</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>VH_bad</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.csv</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IgFold_Full001_full_heavy_FASTA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Full001</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>full_heavy</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>full_heavy</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.fasta</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>FASTA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>IgFold_Full001_full_heavy_CSV</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>IgFold</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Full001</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>full_heavy</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>full_heavy</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>external_inputs\IgFold\IgFold_input.csv</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>local_cli</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>PENDING_MANUAL_RUN</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Exported input file generated. Please run this file manually with the selected external tool and upload the result file back to AbDev-Lite.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>tool_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tool_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tool_category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>antibody_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>chain_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sequence_scope</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>result_status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>result_metric_name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>result_metric_value</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>result_risk_class</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>result_interpretation</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>result_file_name</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>imported_at</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>merge_status</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>merge_warning</t>
         </is>
       </c>
     </row>
@@ -5580,6 +8536,272 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>antibody_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>external_tool_results_available</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tools_with_results</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>humanness_tool_result_available</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>developability_tool_result_available</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>structure_tool_result_available</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>external_high_risk_flags</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>external_medium_risk_flags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>external_low_risk_flags</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>external_tool_summary_text</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>external_tool_review_recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ab001</t>
+        </is>
+      </c>
+      <c r="B2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BadSeq001</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BsAb001</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Full001</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VHH001</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>No external tool result was imported.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -24488,7 +27710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24583,378 +27805,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ab001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>VH</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>VH</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F2" t="n">
-        <v>82</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>IGHV3-23</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>IGHV3-23</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>IGHJ4</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>92</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Imported humanness/germline metrics indicate low human-likeness risk based on conservative review of: humanness_percentile=82.0; framework_identity=92.0; identity_to_human_germline=91.5; closest_species=human. Human-likeness is not equivalent to clinical immunogenicity prediction.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Example imported result; low human-likeness risk by percentile and framework identity.</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>matched_by_antibody_id_chain_id</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ab001</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>VL</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VL</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="F3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>IGKV1-39</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>IGKV1-39</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>IGKJ1</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="M3" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Imported humanness/germline metrics indicate low human-likeness risk based on conservative review of: humanness_percentile=76.0; framework_identity=90.1; identity_to_human_germline=89.2; closest_species=human. Human-likeness is not equivalent to clinical immunogenicity prediction.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Example imported result; low human-likeness risk.</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>matched_by_antibody_id_chain_id</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BsAb001</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>VH_arm1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>VH_arm1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="F4" t="n">
-        <v>55</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>IGHV1-46</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>IGHV1-46</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>IGHJ6</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="M4" t="n">
-        <v>65</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Imported humanness/germline metrics indicate medium human-likeness risk based on conservative review of: humanness_percentile=55.0; framework_identity=81.7; identity_to_human_germline=82.3; closest_species=human. Human-likeness is not equivalent to clinical immunogenicity prediction.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Example imported result; medium risk driven by percentile/framework identity.</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>matched_by_antibody_id_chain_id</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BsAb001</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>VH_arm2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VH_arm2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="F5" t="n">
-        <v>22</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>IGHV4-34</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>mouse</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>IGHV4-34</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>IGHJ3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Imported humanness/germline metrics indicate high human-likeness risk based on conservative review of: humanness_percentile=22.0; framework_identity=68.5; identity_to_human_germline=66.8; closest_species=mouse. Human-likeness is not equivalent to clinical immunogenicity prediction.</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Example imported result; high risk driven by low percentile and framework identity.</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>matched_by_antibody_id_chain_id</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>VHH001</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>VHH</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VHH</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>camelid</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>69</v>
-      </c>
-      <c r="L6" t="n">
-        <v>72</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Imported humanness/germline metrics indicate high human-likeness risk based on conservative review of: framework_identity=72.0; identity_to_human_germline=69.0; closest_species=camelid. Human-likeness is not equivalent to clinical immunogenicity prediction.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Example VHH imported result; non-human species and borderline framework identity require review.</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>matched_by_antibody_id_chain_id</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
